--- a/VerveStacks_BRA_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A931528C-5A6D-45EB-A903-9A8B41BB3ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED5AA40F-2AE4-49C8-B39C-88CF93D06E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2637,7 +2637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D208250F-65C1-465A-ABB8-67EC5A5D89B5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE538CE9-023A-4D5D-8126-27E0C57FE265}">
   <dimension ref="B9:E248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_BRA_grids_kan10/Sets-vervestacks.xlsx
+++ b/VerveStacks_BRA_grids_kan10/Sets-vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED5AA40F-2AE4-49C8-B39C-88CF93D06E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6241723C-1168-4E02-8632-5562013FC847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2637,7 +2637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE538CE9-023A-4D5D-8126-27E0C57FE265}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BD31939-2C05-4783-B175-E4139C905262}">
   <dimension ref="B9:E248"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
